--- a/produits/preuves/sortie/c4-tcd/c4-tcd.xlsx
+++ b/produits/preuves/sortie/c4-tcd/c4-tcd.xlsx
@@ -773,11 +773,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="26553118"/>
-        <c:axId val="54475313"/>
+        <c:axId val="41754869"/>
+        <c:axId val="743400"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="26553118"/>
+        <c:axId val="41754869"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -805,7 +805,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54475313"/>
+        <c:crossAx val="743400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -813,7 +813,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="54475313"/>
+        <c:axId val="743400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -850,7 +850,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26553118"/>
+        <c:crossAx val="41754869"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1175,11 +1175,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="26278071"/>
-        <c:axId val="57928429"/>
+        <c:axId val="19457218"/>
+        <c:axId val="9375364"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="26278071"/>
+        <c:axId val="19457218"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1207,7 +1207,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57928429"/>
+        <c:crossAx val="9375364"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1215,7 +1215,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="57928429"/>
+        <c:axId val="9375364"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1252,7 +1252,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26278071"/>
+        <c:crossAx val="19457218"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
